--- a/docs/测试用例清单_模块一.xlsx
+++ b/docs/测试用例清单_模块一.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob\Desktop\workspace\华科\软件测试与质量保证实践\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C1CDF8-F4F8-472D-A728-41FB4A42A7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ABC53E-D442-4D3E-9080-AB978535D1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5960" yWindow="0" windowWidth="19640" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases测试用例" sheetId="2" r:id="rId1"/>
@@ -689,9 +689,6 @@
     <t>026</t>
   </si>
   <si>
-    <t>eval.py</t>
-  </si>
-  <si>
     <t>评估入口不应使用不安全的eval</t>
   </si>
   <si>
@@ -850,12 +847,16 @@
   <si>
     <t>抛出ValueError并停止处理</t>
   </si>
+  <si>
+    <t>main</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
@@ -897,6 +898,11 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -944,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -961,6 +967,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1570,7 +1579,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>46</v>
@@ -1582,16 +1591,16 @@
         <v>17</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>22</v>
@@ -2386,11 +2395,11 @@
       <c r="A27" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>46</v>
@@ -2402,36 +2411,36 @@
         <v>17</v>
       </c>
       <c r="G27" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="I27" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="J27" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="K27" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>59</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>46</v>
@@ -2443,16 +2452,16 @@
         <v>17</v>
       </c>
       <c r="G28" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="I28" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="J28" s="7" t="s">
         <v>189</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>22</v>
@@ -2466,13 +2475,13 @@
     </row>
     <row r="29" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>33</v>
@@ -2484,16 +2493,16 @@
         <v>17</v>
       </c>
       <c r="G29" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="J29" s="7" t="s">
         <v>195</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>196</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>22</v>
@@ -2507,13 +2516,13 @@
     </row>
     <row r="30" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>33</v>
@@ -2525,16 +2534,16 @@
         <v>17</v>
       </c>
       <c r="G30" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="I30" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="J30" s="7" t="s">
         <v>201</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>202</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>22</v>
@@ -2548,13 +2557,13 @@
     </row>
     <row r="31" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>16</v>
@@ -2566,13 +2575,13 @@
         <v>17</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="I31" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>207</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>130</v>
@@ -2589,13 +2598,13 @@
     </row>
     <row r="32" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>33</v>
@@ -2607,16 +2616,16 @@
         <v>17</v>
       </c>
       <c r="G32" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H32" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="I32" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="J32" s="7" t="s">
         <v>212</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>213</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>22</v>
@@ -2630,13 +2639,13 @@
     </row>
     <row r="33" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>16</v>
@@ -2648,16 +2657,16 @@
         <v>17</v>
       </c>
       <c r="G33" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="I33" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="J33" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>22</v>
@@ -2671,13 +2680,13 @@
     </row>
     <row r="34" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>16</v>
@@ -2689,16 +2698,16 @@
         <v>17</v>
       </c>
       <c r="G34" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H34" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="I34" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="J34" s="7" t="s">
         <v>224</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>225</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>22</v>
